--- a/data/Coastal_Harbor_Export.xlsx
+++ b/data/Coastal_Harbor_Export.xlsx
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -303,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -459,6 +460,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6577,7 +6579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="13.33" customWidth="1" style="56" min="1" max="1"/>
@@ -7368,16 +7370,426 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="56"/>
-    <row r="20" ht="15.75" customHeight="1" s="56"/>
-    <row r="21" ht="15.75" customHeight="1" s="56"/>
-    <row r="22" ht="15.75" customHeight="1" s="56"/>
-    <row r="23" ht="15.75" customHeight="1" s="56"/>
-    <row r="24" ht="15.75" customHeight="1" s="56"/>
-    <row r="25" ht="15.75" customHeight="1" s="56"/>
-    <row r="26" ht="15.75" customHeight="1" s="56"/>
-    <row r="27" ht="15.75" customHeight="1" s="56"/>
-    <row r="28" ht="15.75" customHeight="1" s="56"/>
+    <row r="19" ht="15.75" customHeight="1" s="56">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ent018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tidewater Coffee Roasters</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>llc</t>
+        </is>
+      </c>
+      <c r="D19" s="57" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Specialty coffee roaster with retail café on Main Street</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tidewater Coffee</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>52-3344556</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="56">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ent019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chesapeake Machine Works</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>c_Corp</t>
+        </is>
+      </c>
+      <c r="D20" s="57" t="n">
+        <v>24546</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Precision CNC machining for marine and aerospace parts</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>52-1122334</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="56">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ent020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Harbor Build &amp; Trade</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>llc</t>
+        </is>
+      </c>
+      <c r="D21" s="57" t="n">
+        <v>39764</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>General contractor specializing in dockside and waterfront renovations</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Harbor Build</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>52-2233445</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="56">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ent021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Annapolis Direct Primary Care</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sole_Proprietor</t>
+        </is>
+      </c>
+      <c r="D22" s="57" t="n">
+        <v>42906</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Membership-based primary care clinic</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>520000</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>412-55-7788</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="56">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ent022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bayside Cloud Services</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>c_Corp</t>
+        </is>
+      </c>
+      <c r="D23" s="57" t="n">
+        <v>42248</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Regional B2B cloud-hosting startup; SOC2-Type-2 certified</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>12400000</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bayside Cloud</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>27-9988112</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="56">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ent023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Severn River Yacht Club</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>limited_Partnership</t>
+        </is>
+      </c>
+      <c r="D24" s="57" t="n">
+        <v>20576</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Private yacht club and sailing school on the Severn River</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>52-4455667</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="56">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ent024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Chesapeake Bay Aquarium</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>not_For_Profit</t>
+        </is>
+      </c>
+      <c r="D25" s="57" t="n">
+        <v>32325</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Regional aquarium and marine education nonprofit</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>52-6677889</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="56">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ent025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Eastport Crab Company</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>llc</t>
+        </is>
+      </c>
+      <c r="D26" s="57" t="n">
+        <v>36955</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Seafood wholesaler and steamed-crab retail market</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Eastport Crabs</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>52-5566778</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="56">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ent026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Naptown Brewing</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>c_Corp</t>
+        </is>
+      </c>
+      <c r="D27" s="57" t="n">
+        <v>41684</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Craft brewery and taproom in downtown Annapolis</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Naptown Brewing</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>52-7788990</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="56">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ent027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Harbor Catering</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sole_Proprietor</t>
+        </is>
+      </c>
+      <c r="D28" s="57" t="n">
+        <v>43687</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Event catering spin-off from Coastal Grille &amp; Burgers</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>210000</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Coastal Catering</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>412-55-7790</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="29" ht="15.75" customHeight="1" s="56"/>
     <row r="30" ht="15.75" customHeight="1" s="56"/>
     <row r="31" ht="15.75" customHeight="1" s="56"/>
@@ -8363,7 +8775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.56" customWidth="1" style="56" min="1" max="18"/>
@@ -10689,21 +11101,1111 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="56"/>
-    <row r="34" ht="15.75" customHeight="1" s="56"/>
-    <row r="35" ht="15.75" customHeight="1" s="56"/>
-    <row r="36" ht="15.75" customHeight="1" s="56"/>
-    <row r="37" ht="15.75" customHeight="1" s="56"/>
-    <row r="38" ht="15.75" customHeight="1" s="56"/>
-    <row r="39" ht="15.75" customHeight="1" s="56"/>
-    <row r="40" ht="15.75" customHeight="1" s="56"/>
-    <row r="41" ht="15.75" customHeight="1" s="56"/>
-    <row r="42" ht="15.75" customHeight="1" s="56"/>
-    <row r="43" ht="15.75" customHeight="1" s="56"/>
-    <row r="44" ht="15.75" customHeight="1" s="56"/>
-    <row r="45" ht="15.75" customHeight="1" s="56"/>
-    <row r="46" ht="15.75" customHeight="1" s="56"/>
-    <row r="47" ht="15.75" customHeight="1" s="56"/>
+    <row r="33" ht="15.75" customHeight="1" s="56">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>hum032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Theodore</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Blount</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>hehim</t>
+        </is>
+      </c>
+      <c r="H33" s="57" t="n">
+        <v>22536</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>high_School</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>skilled_Trade_Technician</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1980</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>412-56-7891</t>
+        </is>
+      </c>
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="56">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>hum033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Serrano</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>sheher</t>
+        </is>
+      </c>
+      <c r="H34" s="57" t="n">
+        <v>31931</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>bachelors</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>sales_Marketing</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>hospitality</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>412-67-8912</t>
+        </is>
+      </c>
+      <c r="T34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="56">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hum034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Okafor</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>hehim</t>
+        </is>
+      </c>
+      <c r="H35" s="57" t="n">
+        <v>21882</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>healthcare_Professional</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>healthcare</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1987</v>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>412-78-9123</t>
+        </is>
+      </c>
+      <c r="T35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="56">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hum035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Craig</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Maddox</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Craig</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>hehim</t>
+        </is>
+      </c>
+      <c r="H36" s="57" t="n">
+        <v>26712</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>bachelors</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>manager_Supervisor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>2003</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>412-89-1234</t>
+        </is>
+      </c>
+      <c r="T36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="56">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>hum036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tiffany</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Marsh</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tiff</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>sheher</t>
+        </is>
+      </c>
+      <c r="H37" s="57" t="n">
+        <v>32985</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>bachelors</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>administrator_Clerical</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2015</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>412-91-2345</t>
+        </is>
+      </c>
+      <c r="T37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="56">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>hum037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Hendricks</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>hehim</t>
+        </is>
+      </c>
+      <c r="H38" s="57" t="n">
+        <v>29869</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>high_School</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>laborer</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2002</v>
+      </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>412-12-3456</t>
+        </is>
+      </c>
+      <c r="T38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="56">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>hum038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brandi</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ortiz</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Brandi</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>sheher</t>
+        </is>
+      </c>
+      <c r="H39" s="57" t="n">
+        <v>30871</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>high_School</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>arts_Entertainment_Recreation</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2004</v>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>412-23-4567</t>
+        </is>
+      </c>
+      <c r="T39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="56">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>hum039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Oren</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>hehim</t>
+        </is>
+      </c>
+      <c r="H40" s="57" t="n">
+        <v>28095</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>masters</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>arts</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>2006</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>412-34-5678</t>
+        </is>
+      </c>
+      <c r="T40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="56">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>hum040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mrs.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tamara</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>J.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sutton</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tam</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>sheher</t>
+        </is>
+      </c>
+      <c r="H41" s="57" t="n">
+        <v>25439</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>masters</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>administrator_Clerical</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1996</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>divorced</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>412-45-6789</t>
+        </is>
+      </c>
+      <c r="T41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="56">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>hum041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Leighton</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>sheher</t>
+        </is>
+      </c>
+      <c r="H42" s="57" t="n">
+        <v>26003</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>masters</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>educator_Professor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2001</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>412-56-7892</t>
+        </is>
+      </c>
+      <c r="T42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="56">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>hum042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Macklin</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Burt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>hehim</t>
+        </is>
+      </c>
+      <c r="H43" s="57" t="n">
+        <v>28624</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>bachelors</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>legal_Financial_Professional</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>government</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>412-67-8913</t>
+        </is>
+      </c>
+      <c r="T43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="56">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>hum043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ms.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Stonefield</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>sheher</t>
+        </is>
+      </c>
+      <c r="H44" s="57" t="n">
+        <v>23405</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>bachelors</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>executive_Owner</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1989</v>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>412-78-9124</t>
+        </is>
+      </c>
+      <c r="T44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="56">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>hum044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Pryor</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>hehim</t>
+        </is>
+      </c>
+      <c r="H45" s="57" t="n">
+        <v>30412</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>high_School</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>arts_Entertainment_Recreation</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2004</v>
+      </c>
+      <c r="M45" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>412-89-1235</t>
+        </is>
+      </c>
+      <c r="T45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="56">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>hum045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mrs.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Barkley-Holt</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Jen</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>sheher</t>
+        </is>
+      </c>
+      <c r="H46" s="57" t="n">
+        <v>27448</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>masters</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>sales_Marketing</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>politics</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1999</v>
+      </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>412-91-2346</t>
+        </is>
+      </c>
+      <c r="T46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="56">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>hum046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Perry</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Harper</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Perry</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>hehim</t>
+        </is>
+      </c>
+      <c r="H47" s="57" t="n">
+        <v>24032</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>bachelors</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>information_Media_Communications</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1989</v>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>412-12-3457</t>
+        </is>
+      </c>
+      <c r="T47" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="48" ht="15.75" customHeight="1" s="56"/>
     <row r="49" ht="15.75" customHeight="1" s="56"/>
     <row r="50" ht="15.75" customHeight="1" s="56"/>
@@ -11670,7 +13172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN72"/>
+  <dimension ref="A1:AN97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.56" customWidth="1" style="56" min="1" max="1"/>
@@ -19631,31 +21133,2151 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1" s="56"/>
-    <row r="74" ht="15.75" customHeight="1" s="56"/>
-    <row r="75" ht="15.75" customHeight="1" s="56"/>
-    <row r="76" ht="15.75" customHeight="1" s="56"/>
-    <row r="77" ht="15.75" customHeight="1" s="56"/>
-    <row r="78" ht="15.75" customHeight="1" s="56"/>
-    <row r="79" ht="15.75" customHeight="1" s="56"/>
-    <row r="80" ht="15.75" customHeight="1" s="56"/>
-    <row r="81" ht="15.75" customHeight="1" s="56"/>
-    <row r="82" ht="15.75" customHeight="1" s="56"/>
-    <row r="83" ht="15.75" customHeight="1" s="56"/>
-    <row r="84" ht="15.75" customHeight="1" s="56"/>
-    <row r="85" ht="15.75" customHeight="1" s="56"/>
-    <row r="86" ht="15.75" customHeight="1" s="56"/>
-    <row r="87" ht="15.75" customHeight="1" s="56"/>
-    <row r="88" ht="15.75" customHeight="1" s="56"/>
-    <row r="89" ht="15.75" customHeight="1" s="56"/>
-    <row r="90" ht="15.75" customHeight="1" s="56"/>
-    <row r="91" ht="15.75" customHeight="1" s="56"/>
-    <row r="92" ht="15.75" customHeight="1" s="56"/>
-    <row r="93" ht="15.75" customHeight="1" s="56"/>
-    <row r="94" ht="15.75" customHeight="1" s="56"/>
-    <row r="95" ht="15.75" customHeight="1" s="56"/>
-    <row r="96" ht="15.75" customHeight="1" s="56"/>
-    <row r="97" ht="15.75" customHeight="1" s="56"/>
+    <row r="73" ht="15.75" customHeight="1" s="56">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ent018</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>140 Main Street</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R73" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>140 Main Street</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>4105552018</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>https://tidewatercoffee.example.com</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>hello@tidewatercoffee.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" s="56">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ent019</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2200 Industrial Park Rd</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R74" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2200 Industrial Park Rd</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA74" t="n">
+        <v>4105552019</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>https://chesapeakemachineworks.example.com</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>orders@cmw.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="56">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ent020</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Yard</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>88 Dockside Ln</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R75" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>88 Dockside Ln</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA75" t="n">
+        <v>4105552020</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>https://harborbuild.example.com</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>jobs@harborbuild.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" s="56">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ent021</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Clinic</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>500 West Street</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R76" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>500 West Street</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA76" t="n">
+        <v>4105552021</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>https://annapolisdpc.example.com</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>info@annapolisdpc.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="56">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ent022</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>900 Bay Ridge Ave</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R77" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>900 Bay Ridge Ave</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA77" t="n">
+        <v>4105552022</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>https://baysidecloud.example.com</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>sales@baysidecloud.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" s="56">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ent023</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Clubhouse</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1 Severn Point Rd</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R78" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1 Severn Point Rd</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA78" t="n">
+        <v>4105552023</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>https://severnriveryc.example.com</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>events@severnriveryc.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" s="56">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ent024</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Main Entry</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>50 Aquarium Way</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R79" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>50 Aquarium Way</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA79" t="n">
+        <v>4105552024</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>https://chesapeakebayaquarium.example.com</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>info@chesapeakebayaquarium.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="56">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ent025</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>11 Dock Street</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R80" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>11 Dock Street</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA80" t="n">
+        <v>4105552025</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>https://eastportcrab.example.com</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>orders@eastportcrab.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" s="56">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ent026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Taproom</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>77 West Street</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R81" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>77 West Street</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA81" t="n">
+        <v>4105552026</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>https://naptownbrewing.example.com</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>hello@naptownbrewing.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1" s="56">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ent027</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BUSINESS</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>HQ</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>120 Harbor Dr</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R82" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>120 Harbor Dr</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA82" t="n">
+        <v>4105552027</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC82" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>catering@coastalgrille.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" s="56">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>hum032</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>15 Lumber Ln</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R83" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>15 Lumber Ln</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA83" t="n">
+        <v>4105553032</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>ted.blount@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" s="56">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>hum033</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>220 Dock St</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R84" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>220 Dock St</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA84" t="n">
+        <v>4105553033</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>monica.serrano@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="56">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>hum034</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>500 West Street</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R85" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>500 West Street</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA85" t="n">
+        <v>4105553034</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC85" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>dr.okafor@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="56">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>hum035</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>140 Harbor Dr</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R86" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>140 Harbor Dr</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA86" t="n">
+        <v>4105553035</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>craig.maddox@annapolisparks.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" s="56">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>hum036</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>140 Harbor Dr</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R87" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>140 Harbor Dr</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA87" t="n">
+        <v>4105553036</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC87" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>tiff@annapolis.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1" s="56">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>hum037</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2200 Industrial Park Rd</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R88" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>2200 Industrial Park Rd</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA88" t="n">
+        <v>4105553037</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>kyle.h@cmw.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1" s="56">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>hum038</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>220 Dock St</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R89" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>220 Dock St</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA89" t="n">
+        <v>4105553038</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC89" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>brandi.ortiz@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1" s="56">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>hum039</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>77 Artisan Way</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R90" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>77 Artisan Way</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA90" t="n">
+        <v>4105553039</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>oren@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1" s="56">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>hum040</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>900 Library Row</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R91" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>900 Library Row</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA91" t="n">
+        <v>4105553040</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>tamara@annapolislib.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1" s="56">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>hum041</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1 College Ave</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R92" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1 College Ave</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA92" t="n">
+        <v>4105553041</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>diana.leighton@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1" s="56">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>hum042</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>140 Harbor Dr</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R93" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>140 Harbor Dr</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA93" t="n">
+        <v>4105553042</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC93" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>burt.macklin@annapolis.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1" s="56">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>hum043</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2200 Industrial Park Rd</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R94" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>2200 Industrial Park Rd</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA94" t="n">
+        <v>4105553043</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC94" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>evelyn@cmw.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1" s="56">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>hum044</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>18 Waterman Way</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R95" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>18 Waterman Way</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA95" t="n">
+        <v>4105553044</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC95" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>drew.pryor@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1" s="56">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>hum045</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>450 Campaign Ln</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R96" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>450 Campaign Ln</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA96" t="n">
+        <v>4105553045</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>jen.holt@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1" s="56">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>hum046</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I97" t="b">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>100 Press Row</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="R97" s="57" t="n">
+        <v>43101</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>100 Press Row</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Annapolis</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="AA97" t="n">
+        <v>4105553046</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>perry@annapolissentinel.example.com</t>
+        </is>
+      </c>
+    </row>
     <row r="98" ht="15.75" customHeight="1" s="56"/>
     <row r="99" ht="15.75" customHeight="1" s="56"/>
     <row r="100" ht="15.75" customHeight="1" s="56"/>
@@ -20588,7 +24210,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.56" customWidth="1" style="56" min="1" max="1"/>
@@ -22311,26 +25933,606 @@
       <c r="E60" s="51" t="n"/>
       <c r="F60" s="53" t="n"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="56"/>
-    <row r="62" ht="15.75" customHeight="1" s="56"/>
-    <row r="63" ht="15.75" customHeight="1" s="56"/>
-    <row r="64" ht="15.75" customHeight="1" s="56"/>
-    <row r="65" ht="15.75" customHeight="1" s="56"/>
-    <row r="66" ht="15.75" customHeight="1" s="56"/>
-    <row r="67" ht="15.75" customHeight="1" s="56"/>
-    <row r="68" ht="15.75" customHeight="1" s="56"/>
-    <row r="69" ht="15.75" customHeight="1" s="56"/>
-    <row r="70" ht="15.75" customHeight="1" s="56"/>
-    <row r="71" ht="15.75" customHeight="1" s="56"/>
-    <row r="72" ht="15.75" customHeight="1" s="56"/>
-    <row r="73" ht="15.75" customHeight="1" s="56"/>
-    <row r="74" ht="15.75" customHeight="1" s="56"/>
-    <row r="75" ht="15.75" customHeight="1" s="56"/>
-    <row r="76" ht="15.75" customHeight="1" s="56"/>
-    <row r="77" ht="15.75" customHeight="1" s="56"/>
-    <row r="78" ht="15.75" customHeight="1" s="56"/>
-    <row r="79" ht="15.75" customHeight="1" s="56"/>
-    <row r="80" ht="15.75" customHeight="1" s="56"/>
+    <row r="61" ht="15.75" customHeight="1" s="56">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Monica Serrano</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Owner of</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Tidewater Coffee Roasters</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" s="56">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tidewater Coffee Roasters</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Owned by</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Monica Serrano</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" s="56">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Chesapeake Machine Works</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Subsidiary of</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Stonefield Confections</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" s="56">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kyle Hendricks</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Employee of</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Chesapeake Machine Works</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" s="56">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Chesapeake Machine Works</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Employer of</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Kyle Hendricks</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="56">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Evelyn Stonefield</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Owner of</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Chesapeake Machine Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" s="56">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Theodore Blount</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Employee of</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Harbor Build &amp; Trade</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" s="56">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Harbor Build &amp; Trade</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Employer of</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Theodore Blount</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Foreman</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" s="56">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Richard Okafor</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Owner of</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Annapolis Direct Primary Care</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" s="56">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Annapolis Direct Primary Care</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Owned by</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Richard Okafor</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" s="56">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Craig Maddox</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Employee of</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Annapolis Parks Department</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Assistant Director</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1" s="56">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Annapolis Parks Department</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Employer of</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Craig Maddox</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Assistant Director</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="56">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tiffany Marsh</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Employee of</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Annapolis Parks Department</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" s="56">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Diana Leighton</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Employee of</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Severn River Yacht Club</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Sailing Instructor</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="56">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tamara Sutton</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Employee of</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Chesapeake Historical Society</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" s="56">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Burton Macklin</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Employee of</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Annapolis Parks Department</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="56">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Andrew Pryor</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Co-Worker of</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Drew Pryor</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" s="56">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Perry Harper</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Employee of</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>The Annapolis Sentinel</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" s="56">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>The Annapolis Sentinel</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Employer of</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Perry Harper</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="56">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Jennifer Barkley-Holt</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Consultant to</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Bayside Cloud Services</t>
+        </is>
+      </c>
+    </row>
     <row r="81" ht="15.75" customHeight="1" s="56"/>
     <row r="82" ht="15.75" customHeight="1" s="56"/>
     <row r="83" ht="15.75" customHeight="1" s="56"/>
